--- a/docs/Pathway-enrichment/Pathway-enrichment-for-genes-with-DARs-downin-Healthy.vs.Patients.xlsx
+++ b/docs/Pathway-enrichment/Pathway-enrichment-for-genes-with-DARs-downin-Healthy.vs.Patients.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="271">
   <si>
     <t xml:space="preserve">Term</t>
   </si>
@@ -32,391 +32,499 @@
     <t xml:space="preserve">P.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">protease binding</t>
+    <t xml:space="preserve">protein binding</t>
   </si>
   <si>
     <t xml:space="preserve">MF</t>
   </si>
   <si>
-    <t xml:space="preserve">SMAD binding</t>
+    <t xml:space="preserve">binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular_function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaling receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">growth factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein-containing complex binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphoprotein binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphotyrosine residue binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein phosphorylated amino acid binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enzyme regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTPase regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nucleoside-triphosphatase regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular function activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molecular function regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insulin-like growth factor II binding</t>
   </si>
   <si>
     <t xml:space="preserve">enzyme binding</t>
   </si>
   <si>
-    <t xml:space="preserve">cyclic pyranopterin monophosphate synthase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTP 3',8'-cyclase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MH1 domain binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glucuronosyltransferase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">histone deacetylase binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deacetylase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">growth factor binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nucleosomal DNA binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G protein-coupled UDP receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inositol-1,3,4-trisphosphate 4-phosphatase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inositol-3,4-bisphosphate 4-phosphatase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MH2 domain binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylinositol-3,4-bisphosphate 4-phosphatase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADP-ribosylglutamate hydrolase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G protein-coupled ADP receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G protein-coupled UTP receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transcription regulator activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G protein-coupled pyrimidinergic nucleotide receptor activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N-acetylgalactosaminyl-proteoglycan 3-beta-glucuronosyltransferase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phosphatidylinositol-3,4-bisphosphate phosphatase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">purine-rich negative regulatory element binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ryanodine-sensitive calcium-release channel activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deacylase activity</t>
+    <t xml:space="preserve">guanyl-nucleotide exchange factor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beta-catenin binding</t>
   </si>
   <si>
     <t xml:space="preserve">transcription corepressor activity</t>
   </si>
   <si>
-    <t xml:space="preserve">regulation of hydrolase activity</t>
+    <t xml:space="preserve">enzyme activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identical protein binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collagen binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein tyrosine kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D5 dopamine receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glutathione dehydrogenase (ascorbate) activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">methylarsonate reductase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parathyroid hormone receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inositol trisphosphate phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dopamine receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nuclear retinoic acid receptor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytokine binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">low-density lipoprotein particle binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTPase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphotransferase activity, alcohol group as acceptor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extracellular matrix structural constituent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adiponectin binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidoreductase activity, acting on a sulfur group of donors, quinone or similar compound as acceptor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidoreductase activity, acting on phosphorus or arsenic in donors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oxidoreductase activity, acting on phosphorus or arsenic in donors, disulfide as acceptor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell adhesion molecule binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small GTPase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ankyrin binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">insulin-like growth factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inositol-polyphosphate 5-phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signaling receptor regulator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inositol phosphate phosphatase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lipoprotein particle binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein-lipid complex binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">superoxide-generating NADPH oxidase activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein phosphatase activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein kinase binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transcription factor binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gap junction hemi-channel activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lactoperoxidase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">protein tyrosine phosphatase activator activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-protein beta/gamma-subunit complex binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hormone binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin binding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transmembrane receptor protein kinase activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytokine receptor activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell communication</t>
   </si>
   <si>
     <t xml:space="preserve">BP</t>
   </si>
   <si>
-    <t xml:space="preserve">regulation of catalytic activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of canonical Wnt signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of proteolysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cellular response to purine-containing compound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of endopeptidase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">connective tissue development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sensory perception of sound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of Wnt signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sensory perception of mechanical stimulus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of peptidase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skeletal system development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of molecular function</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cartilage development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of JNK cascade</t>
+    <t xml:space="preserve">signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular signaling cassette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of intracellular signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemopoiesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell surface receptor signaling pathway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anatomical structure development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell population proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell population proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of small GTPase mediated signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">multicellular organism development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mononuclear cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of biological process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biological regulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cytokine production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">small GTPase-mediated signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-beta T cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cellular process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of lymphocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytokine production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of signaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to peptide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of response to stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to cytokine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of leukocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phagocytosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of peptidyl-tyrosine phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peptidyl-tyrosine phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">peptidyl-tyrosine modification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cytokine production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha-beta T cell activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immune system process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tissue development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell motility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">response to external stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of intracellular signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to cytokine stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">system development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">myeloid cell differentiation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of immune system process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endocytosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of phosphate metabolic process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of phosphorus metabolic process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of developmental process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locomotion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of multicellular organismal process</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of response to external stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular response to chemical stimulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of peptidyl-tyrosine phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lymphocyte activation involved in immune response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell population proliferation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regulation of phosphorylation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin cytoskeleton organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of response to stimulus</t>
   </si>
   <si>
     <t xml:space="preserve">bone development</t>
   </si>
   <si>
-    <t xml:space="preserve">protein maturation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">maintenance of location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of biosynthetic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chondrocyte proliferation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of blood coagulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of hemostasis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone maturation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chondrocyte differentiation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of microtubule depolymerization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of coagulation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anterior semicircular canal development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beta-catenin destruction complex assembly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cellular response to pyrimidine ribonucleotide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lambdoid suture morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lateral ganglionic eminence cell proliferation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lateral semicircular canal development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mesodermal-endodermal cell signaling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">post-embryonic hindlimb morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">response to pyrimidine ribonucleotide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sagittal suture morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subpallium cell proliferation in forebrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">animal organ maturation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">intracellular signaling cassette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epigenetic programming of gene expression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of microtubule depolymerization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of proteasomal ubiquitin-dependent protein catabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of canonical Wnt signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of MAPK cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skeletal muscle fiber development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of JNK cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of macromolecule metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of endopeptidase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">protein metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inositol phosphate metabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">myotube cell development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of microtubule polymerization or depolymerization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activation of blood coagulation via clotting cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fibroblast growth factor receptor apoptotic signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Golgi vesicle fusion to target membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">larynx development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">larynx morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of DNA-templated DNA replication initiation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">respiratory basal cell differentiation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smoothened signaling pathway involved in spinal cord motor neuron cell fate specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">epigenetic regulation of gene expression</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of catalytic activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anatomical structure morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of transcription by RNA polymerase II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proteolysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of proteolysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">microtubule depolymerization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">negative regulation of peptidase activity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical Wnt signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of ubiquitin-dependent protein catabolic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">striated muscle cell development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">activation of plasma proteins involved in acute inflammatory response</t>
-  </si>
-  <si>
-    <t xml:space="preserve">axial mesoderm formation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mammary gland specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nose morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peptidyl-glutamate ADP-deribosylation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">post-embryonic appendage morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">post-embryonic limb morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smoothened signaling pathway involved in ventral spinal cord interneuron specification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smoothened signaling pathway involved in ventral spinal cord patterning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skeletal muscle tissue development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signaling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of Wnt signaling pathway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell communication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of protein processing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of primary metabolic process</t>
+    <t xml:space="preserve">animal organ development</t>
   </si>
   <si>
     <t xml:space="preserve">blood vessel development</t>
   </si>
   <si>
-    <t xml:space="preserve">muscle organ development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skeletal muscle organ development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JNK cascade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of macromolecule biosynthetic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">striated muscle contraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">axial mesoderm morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">frontal suture morphogenesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">positive regulation of inositol trisphosphate biosynthetic process</t>
-  </si>
-  <si>
-    <t xml:space="preserve">principal sensory nucleus of trigeminal nerve development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regulation of inositol trisphosphate biosynthetic process</t>
+    <t xml:space="preserve">import into cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leukocyte activation involved in immune response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of cell communication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negative regulation of signal transduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of cell-cell adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">positive regulation of lymphocyte activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD4-positive, alpha-beta T cell differentiation</t>
   </si>
   <si>
     <t xml:space="preserve">cell periphery</t>
@@ -425,37 +533,298 @@
     <t xml:space="preserve">CC</t>
   </si>
   <si>
+    <t xml:space="preserve">plasma membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasmic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anchoring junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">side of membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin cytoskeleton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lytic vacuole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">external side of plasma membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vacuole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">focal adhesion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell-substrate junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ficolin-1-rich granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endocytic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasmic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endocytic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bounding membrane of organelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endomembrane system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vesicle membrane</t>
+  </si>
+  <si>
     <t xml:space="preserve">collagen-containing extracellular matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">plasma membrane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sarcolemma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ryanodine receptor complex</t>
-  </si>
-  <si>
     <t xml:space="preserve">extracellular matrix</t>
   </si>
   <si>
     <t xml:space="preserve">external encapsulating structure</t>
   </si>
   <si>
-    <t xml:space="preserve">GLI-SUFU complex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">internode region of axon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senescence-associated heterochromatin focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">terminal cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lateral plasma membrane</t>
+    <t xml:space="preserve">ruffle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endosome membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plasma membrane region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vacuolar lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ficolin-1-rich granule membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell leading edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endolysosome lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane raft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">membrane microdomain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">node of Ranvier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phagocytic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transport vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actin filament</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell-cell junction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integrin alpha9-beta1 complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postsynaptic cytoskeleton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">main axon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extracellular space</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clathrin-coated vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytosol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coated vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immunological synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clathrin-coated vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory granule membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postsynapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">melanosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pigment granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transport vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sarcoplasm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tertiary granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platelet alpha granule lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phagocytic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lysosomal lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leading edge membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postsynaptic actin cytoskeleton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMAD protein complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asymmetric synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fc-gamma receptor III complex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mast cell granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postsynaptic density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruffle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coated vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secretory granule lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vacuolar proton-transporting V-type ATPase, V0 domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golgi apparatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cytoplasmic vesicle lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vesicle lumen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cellular anatomical structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intracellular anatomical structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">neuron to neuron synapse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actomyosin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platelet alpha granule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">postsynaptic specialization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exocytic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">synaptic vesicle membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">early endosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sarcoplasmic reticulum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell projection membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extracellular exosome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clathrin-sculpted vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proton-transporting two-sector ATPase complex, proton-transporting domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proton-transporting V-type ATPase, V0 domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extracellular region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lumenal side of endoplasmic reticulum membrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exocytic vesicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">axon initial segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basement membrane</t>
   </si>
   <si>
     <t xml:space="preserve">Pathway</t>
@@ -812,13 +1181,13 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>136</v>
+        <v>14778</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>628</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000210844482780378</v>
+        <v>0.00000000000427656593993223</v>
       </c>
     </row>
     <row r="3">
@@ -829,13 +1198,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>17098</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000665200230665927</v>
+        <v>0.0000000193953341070986</v>
       </c>
     </row>
     <row r="4">
@@ -846,13 +1215,13 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2088</v>
+        <v>18639</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>730</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00123537756193883</v>
+        <v>0.00000007898617755264</v>
       </c>
     </row>
     <row r="5">
@@ -863,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1545</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.000000612100172983021</v>
       </c>
     </row>
     <row r="6">
@@ -880,13 +1249,13 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000028063404404483</v>
       </c>
     </row>
     <row r="7">
@@ -897,13 +1266,13 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>1302</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.00000286750350777079</v>
       </c>
     </row>
     <row r="8">
@@ -914,13 +1283,13 @@
         <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00245232518427482</v>
+        <v>0.00000787011966341372</v>
       </c>
     </row>
     <row r="9">
@@ -931,13 +1300,13 @@
         <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00260892224659898</v>
+        <v>0.0000476359846881995</v>
       </c>
     </row>
     <row r="10">
@@ -948,13 +1317,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00289936075818093</v>
+        <v>0.000054935499493199</v>
       </c>
     </row>
     <row r="11">
@@ -965,13 +1334,13 @@
         <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>1351</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00316581308100965</v>
+        <v>0.0000597119393808092</v>
       </c>
     </row>
     <row r="12">
@@ -982,13 +1351,13 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>42</v>
+        <v>489</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00372266732285532</v>
+        <v>0.0000753101667793041</v>
       </c>
     </row>
     <row r="13">
@@ -999,13 +1368,13 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>490</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.0000784862898995857</v>
       </c>
     </row>
     <row r="14">
@@ -1016,13 +1385,13 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1189</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.0000806157837755184</v>
       </c>
     </row>
     <row r="15">
@@ -1033,13 +1402,13 @@
         <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>2249</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.0000831816515928831</v>
       </c>
     </row>
     <row r="16">
@@ -1050,13 +1419,13 @@
         <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00011536197301175</v>
       </c>
     </row>
     <row r="17">
@@ -1067,13 +1436,13 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>2088</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>109</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.000131506335599137</v>
       </c>
     </row>
     <row r="18">
@@ -1084,13 +1453,13 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.000135845194617301</v>
       </c>
     </row>
     <row r="19">
@@ -1101,13 +1470,13 @@
         <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.000146440870287527</v>
       </c>
     </row>
     <row r="20">
@@ -1118,13 +1487,13 @@
         <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>204</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00021572138308725</v>
       </c>
     </row>
     <row r="21">
@@ -1135,13 +1504,13 @@
         <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>1940</v>
+        <v>625</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00739856436643624</v>
+        <v>0.000299747073452927</v>
       </c>
     </row>
     <row r="22">
@@ -1152,13 +1521,13 @@
         <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.000321720261342899</v>
       </c>
     </row>
     <row r="23">
@@ -1169,13 +1538,13 @@
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>2217</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.000809225367548858</v>
       </c>
     </row>
     <row r="24">
@@ -1186,13 +1555,13 @@
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>565</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00114980083712977</v>
       </c>
     </row>
     <row r="25">
@@ -1203,13 +1572,13 @@
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00130822354821411</v>
       </c>
     </row>
     <row r="26">
@@ -1220,13 +1589,13 @@
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00132203329604271</v>
       </c>
     </row>
     <row r="27">
@@ -1237,13 +1606,13 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00871459826694485</v>
+        <v>0.00136608107415366</v>
       </c>
     </row>
     <row r="28">
@@ -1254,13 +1623,625 @@
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.00136608107415366</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00136608107415366</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.00136608107415366</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.00138094918273487</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00182837549093679</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="n">
+        <v>25</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.00195932220983491</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" t="n">
+        <v>144</v>
+      </c>
+      <c r="D34" t="n">
+        <v>13</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0026966929830388</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D35" t="n">
+        <v>4</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.00300565945037583</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>315</v>
+      </c>
+      <c r="D36" t="n">
+        <v>22</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.00341027832585671</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>672</v>
+      </c>
+      <c r="D37" t="n">
+        <v>39</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.00384551472490646</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" t="n">
+        <v>168</v>
+      </c>
+      <c r="D38" t="n">
+        <v>14</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.00392810952929976</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" t="n">
         <v>3</v>
       </c>
-      <c r="E28" t="n">
-        <v>0.00972215802985155</v>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>567</v>
+      </c>
+      <c r="D43" t="n">
+        <v>34</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.00409121375272</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>283</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0044721168414118</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" t="n">
+        <v>19</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.00461579522793883</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" t="n">
+        <v>19</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.00461579522793883</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" t="n">
+        <v>726</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.00493031820324847</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.00497594659010011</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" t="n">
+        <v>598</v>
+      </c>
+      <c r="D49" t="n">
+        <v>35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0052604375648113</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.00560315983418469</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" t="n">
+        <v>32</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0060015311082618</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" t="n">
+        <v>32</v>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0060015311082618</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" t="n">
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.00665536430702135</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" t="n">
+        <v>21</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.00672198689988207</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" t="n">
+        <v>699</v>
+      </c>
+      <c r="D55" t="n">
+        <v>39</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.00728939693524371</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" t="n">
+        <v>592</v>
+      </c>
+      <c r="D56" t="n">
+        <v>34</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.00777511180908418</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.00779888654807101</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.00779888654807101</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.00779888654807101</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="n">
+        <v>22</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.00797921271402225</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="n">
+        <v>94</v>
+      </c>
+      <c r="D61" t="n">
+        <v>9</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.00799391712361601</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>66</v>
+      </c>
+      <c r="B62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>443</v>
+      </c>
+      <c r="D62" t="n">
+        <v>27</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.00801280973981496</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>78</v>
+      </c>
+      <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.00809899990420852</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" t="n">
+        <v>96</v>
+      </c>
+      <c r="D64" t="n">
+        <v>9</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.00913391040146169</v>
       </c>
     </row>
   </sheetData>
@@ -1293,1702 +2274,1702 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C2" t="n">
-        <v>334</v>
+        <v>6749</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>354</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0000783365863486709</v>
+        <v>0.00000000000000100829875505913</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>882</v>
+        <v>6724</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>352</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000945725237541521</v>
+        <v>0.00000000000000184016701291973</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C4" t="n">
-        <v>149</v>
+        <v>6216</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000298801334364582</v>
+        <v>0.0000000000000150750498979507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>430</v>
+        <v>3045</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00030869975612924</v>
+        <v>0.0000000000000502993392890682</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>4221</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000350946442956648</v>
+        <v>0.00000000000042213436844895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>66</v>
+        <v>3185</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000392544511524587</v>
+        <v>0.000000000000937985144823427</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>291</v>
+        <v>3635</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>212</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00039845330728125</v>
+        <v>0.00000000000100094684973954</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>169</v>
+        <v>7631</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>376</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000481556866215843</v>
+        <v>0.00000000000134262243787233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>3628</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>211</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000623265165545713</v>
+        <v>0.0000000000015357828173651</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>1956</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>133</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000839228066669479</v>
+        <v>0.00000000000244358500883627</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>3125</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>182</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000880931862274417</v>
+        <v>0.0000000000888986593662078</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C13" t="n">
-        <v>541</v>
+        <v>2029</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00103127925653455</v>
+        <v>0.000000000253134448467421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C14" t="n">
-        <v>1483</v>
+        <v>639</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00104169818489576</v>
+        <v>0.000000000295502810845089</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C15" t="n">
-        <v>210</v>
+        <v>6708</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>328</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00108416850499398</v>
+        <v>0.000000000504173522577689</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C16" t="n">
-        <v>3685</v>
+        <v>977</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00112801573215203</v>
+        <v>0.00000000069123518142861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C17" t="n">
-        <v>97</v>
+        <v>1153</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="E17" t="n">
-        <v>0.00120707253608018</v>
+        <v>0.000000000872732476452603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C18" t="n">
-        <v>219</v>
+        <v>2932</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00126586017571182</v>
+        <v>0.00000000117512284740656</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C19" t="n">
-        <v>565</v>
+        <v>5906</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>294</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00128885891827422</v>
+        <v>0.00000000132242669190969</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C20" t="n">
-        <v>224</v>
+        <v>6120</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00137552122598623</v>
+        <v>0.00000000173731612172099</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C21" t="n">
-        <v>2749</v>
+        <v>831</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
-        <v>0.00143458715423381</v>
+        <v>0.00000000179304367231698</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C22" t="n">
-        <v>26</v>
+        <v>9311</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>425</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00143637551612946</v>
+        <v>0.00000000183054729341779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C23" t="n">
-        <v>227</v>
+        <v>1720</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0014444176500765</v>
+        <v>0.00000000224572619383987</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C24" t="n">
-        <v>27</v>
+        <v>7594</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>357</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00154915645103477</v>
+        <v>0.00000000635901251795424</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C25" t="n">
-        <v>27</v>
+        <v>1786</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="E25" t="n">
-        <v>0.00154915645103477</v>
+        <v>0.00000000946424568478347</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C26" t="n">
-        <v>29</v>
+        <v>12399</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>533</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00178698746666571</v>
+        <v>0.00000000964927814537401</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C27" t="n">
-        <v>116</v>
+        <v>1000</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>0.00201658171159993</v>
+        <v>0.0000000100682403038103</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>2093</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00204106138650069</v>
+        <v>0.0000000221038899051164</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>5700</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>279</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00204106138650069</v>
+        <v>0.0000000282657420881399</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000320384663898864</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>4852</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>244</v>
       </c>
       <c r="E31" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000366243519795939</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>533</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E32" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000367567508673026</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E33" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000372673067414075</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>6422</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000390806589573631</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>12011</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>516</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000408110980997541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>4532</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000531830702365959</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>4534</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000552256670503761</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>1551</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000586364212007407</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>597</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000689119282600237</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>653</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00216138328530269</v>
+        <v>0.0000000771232448334084</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C41" t="n">
-        <v>33</v>
+        <v>12800</v>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>542</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00231123980645491</v>
+        <v>0.0000000871683148135902</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C42" t="n">
-        <v>1956</v>
+        <v>514</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E42" t="n">
-        <v>0.00245847620002624</v>
+        <v>0.0000000887720802639695</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C43" t="n">
-        <v>35</v>
+        <v>487</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00259738516889737</v>
+        <v>0.000000135933707107215</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C44" t="n">
-        <v>37</v>
+        <v>819</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00289936075818093</v>
+        <v>0.000000170915885318774</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C45" t="n">
-        <v>132</v>
+        <v>1650</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00291007639650051</v>
+        <v>0.0000001726137210311</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C46" t="n">
-        <v>277</v>
+        <v>138</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00297584705618707</v>
+        <v>0.000000179229967027092</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C47" t="n">
-        <v>464</v>
+        <v>6054</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>288</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00315572669819056</v>
+        <v>0.000000244930432541713</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>521</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00321703069619396</v>
+        <v>0.000000338817339231705</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C49" t="n">
-        <v>139</v>
+        <v>902</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0033664077218711</v>
+        <v>0.000000471424149251191</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C50" t="n">
-        <v>3374</v>
+        <v>1822</v>
       </c>
       <c r="D50" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00362912209676392</v>
+        <v>0.000000568149852187373</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>1031</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>0.00372266732285532</v>
+        <v>0.000000685245629374054</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C52" t="n">
-        <v>4486</v>
+        <v>2411</v>
       </c>
       <c r="D52" t="n">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0038737721054444</v>
+        <v>0.00000075927463232942</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C53" t="n">
-        <v>43</v>
+        <v>1016</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0038989142670987</v>
+        <v>0.000000818917432776418</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C54" t="n">
-        <v>43</v>
+        <v>593</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0038989142670987</v>
+        <v>0.000000837154739291119</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C55" t="n">
-        <v>44</v>
+        <v>238</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00407898412239143</v>
+        <v>0.000000863178160216136</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>2578</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="E56" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.000000907001632421872</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="B57" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1821</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>107</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.000000977974654364249</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1609</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000110886652462945</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000126349833729137</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000126867410084486</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>199</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000138539439689835</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>892</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="E62" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000142484761708247</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.00000144395655953049</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C64" t="n">
-        <v>308</v>
+        <v>201</v>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00434315588179197</v>
+        <v>0.00000164882626273895</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C65" t="n">
-        <v>504</v>
+        <v>2976</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>157</v>
       </c>
       <c r="E65" t="n">
-        <v>0.00448439037815456</v>
+        <v>0.00000165387978580442</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C66" t="n">
-        <v>2809</v>
+        <v>2066</v>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="E66" t="n">
-        <v>0.005211682365638</v>
+        <v>0.00000177941584760983</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>1266</v>
+        <v>1915</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="E67" t="n">
-        <v>0.00526026837693452</v>
+        <v>0.00000197960152505938</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C68" t="n">
-        <v>1552</v>
+        <v>2523</v>
       </c>
       <c r="D68" t="n">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00531279655215301</v>
+        <v>0.00000199034719988279</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C69" t="n">
-        <v>165</v>
+        <v>1124</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00543421799017709</v>
+        <v>0.00000201753302553736</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C70" t="n">
-        <v>51</v>
+        <v>922</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E70" t="n">
-        <v>0.00544512689168796</v>
+        <v>0.00000205927858177479</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>52</v>
+        <v>4180</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="E71" t="n">
-        <v>0.00565518681878239</v>
+        <v>0.00000210125629989327</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C72" t="n">
-        <v>333</v>
+        <v>437</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E72" t="n">
-        <v>0.00571565693028218</v>
+        <v>0.00000274705375001607</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="B73" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C73" t="n">
-        <v>770</v>
+        <v>455</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E73" t="n">
-        <v>0.00597772431753122</v>
+        <v>0.00000279548922303355</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C74" t="n">
-        <v>172</v>
+        <v>1666</v>
       </c>
       <c r="D74" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00609596218232315</v>
+        <v>0.0000028358994006564</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C75" t="n">
-        <v>174</v>
+        <v>717</v>
       </c>
       <c r="D75" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="E75" t="n">
-        <v>0.00629349924360465</v>
+        <v>0.00000309681933198206</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="B76" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>493</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E76" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000312834351461957</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>493</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E77" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000312834351461957</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>1391</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000324305352396626</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="B79" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1371</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000336095665626341</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="B80" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>513</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E80" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000342891538514044</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1249</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E81" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000385844402532472</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C82" t="n">
-        <v>3</v>
+        <v>1167</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E82" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000405495466228384</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C83" t="n">
-        <v>3</v>
+        <v>2264</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>124</v>
       </c>
       <c r="E83" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000444146367507699</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>1028</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E84" t="n">
-        <v>0.00647045533835655</v>
+        <v>0.00000483040845891028</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C85" t="n">
-        <v>178</v>
+        <v>2894</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="E85" t="n">
-        <v>0.00669998897018859</v>
+        <v>0.00000514404723298225</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C86" t="n">
-        <v>6724</v>
+        <v>156</v>
       </c>
       <c r="D86" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E86" t="n">
-        <v>0.00672060553814735</v>
+        <v>0.00000523127619259404</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C87" t="n">
-        <v>350</v>
+        <v>231</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E87" t="n">
-        <v>0.00679868656440489</v>
+        <v>0.00000542957362136848</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C88" t="n">
-        <v>6749</v>
+        <v>992</v>
       </c>
       <c r="D88" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="E88" t="n">
-        <v>0.00706525768716358</v>
+        <v>0.00000566338309528475</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C89" t="n">
-        <v>60</v>
+        <v>694</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E89" t="n">
-        <v>0.00746662978254938</v>
+        <v>0.00000576392085403749</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C90" t="n">
-        <v>5548</v>
+        <v>733</v>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00750720925264099</v>
+        <v>0.00000580552282293266</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C91" t="n">
-        <v>821</v>
+        <v>1830</v>
       </c>
       <c r="D91" t="n">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="E91" t="n">
-        <v>0.00810060539470777</v>
+        <v>0.00000626153464349628</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C92" t="n">
-        <v>369</v>
+        <v>219</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E92" t="n">
-        <v>0.00816166522116413</v>
+        <v>0.00000708601136071477</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C93" t="n">
-        <v>192</v>
+        <v>3101</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>159</v>
       </c>
       <c r="E93" t="n">
-        <v>0.00824444600703324</v>
+        <v>0.00000732312998753547</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C94" t="n">
-        <v>193</v>
+        <v>821</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E94" t="n">
-        <v>0.00836211062264887</v>
+        <v>0.00000813219401562899</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C95" t="n">
-        <v>2629</v>
+        <v>943</v>
       </c>
       <c r="D95" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E95" t="n">
-        <v>0.00837738797452841</v>
+        <v>0.00000843798761410399</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C96" t="n">
-        <v>194</v>
+        <v>319</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E96" t="n">
-        <v>0.00848076523502786</v>
+        <v>0.00000850636151671777</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>1557</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="E97" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000861781774036427</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>1449</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E98" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000874342258159426</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>337</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E99" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000903911288034964</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>337</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000903911288034964</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E101" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000921032116182643</v>
       </c>
     </row>
   </sheetData>
@@ -3021,206 +4002,1685 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C2" t="n">
         <v>6433</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>330</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00142223375969426</v>
+        <v>0.000000000000688743294146034</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C3" t="n">
-        <v>432</v>
+        <v>5945</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>301</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00231957147043428</v>
+        <v>0.0000000000936333431949127</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C4" t="n">
-        <v>5945</v>
+        <v>2559</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00305499713602794</v>
+        <v>0.00000000133444413317774</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C5" t="n">
-        <v>143</v>
+        <v>2551</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00364576791016604</v>
+        <v>0.0000000035355126848876</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>2397</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00431819858633342</v>
+        <v>0.0000000639015552273095</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>568</v>
+        <v>1093</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00737866759277459</v>
+        <v>0.000000176096571894577</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>569</v>
+        <v>914</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00743223557859431</v>
+        <v>0.000000743985323848711</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>742</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.000000818324870552125</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>909</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000128619626682373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>4206</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000143018366436969</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>909</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00861816295759921</v>
+        <v>0.00000531536229341009</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>12333</v>
       </c>
       <c r="D13" t="n">
+        <v>514</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.00000731496635632079</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" t="n">
+        <v>530</v>
+      </c>
+      <c r="D14" t="n">
+        <v>41</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.00000758817574297809</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9718</v>
+      </c>
+      <c r="D15" t="n">
+        <v>418</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.00000975118881168351</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" t="n">
+        <v>774</v>
+      </c>
+      <c r="D16" t="n">
+        <v>53</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0000127962469925276</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" t="n">
+        <v>774</v>
+      </c>
+      <c r="D17" t="n">
+        <v>53</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0000127962469925276</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" t="n">
+        <v>401</v>
+      </c>
+      <c r="D18" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0000169189289458388</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" t="n">
+        <v>869</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0000210062460222558</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" t="n">
+        <v>424</v>
+      </c>
+      <c r="D20" t="n">
+        <v>34</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0000216750753089583</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="n">
+        <v>434</v>
+      </c>
+      <c r="D21" t="n">
+        <v>34</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0000348468656608315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" t="n">
+        <v>185</v>
+      </c>
+      <c r="D22" t="n">
+        <v>19</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.0000590595743669343</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" t="n">
+        <v>358</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0000716274070808766</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1253</v>
+      </c>
+      <c r="D24" t="n">
+        <v>73</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0000784746267205388</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" t="n">
+        <v>207</v>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0000900069766762026</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2246</v>
+      </c>
+      <c r="D26" t="n">
+        <v>116</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.000120623171084983</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4825</v>
+      </c>
+      <c r="D27" t="n">
+        <v>222</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.000124348556931944</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D28" t="n">
+        <v>73</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.000130977794318501</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B29" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" t="n">
+        <v>432</v>
+      </c>
+      <c r="D29" t="n">
+        <v>32</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00016618190910505</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>199</v>
+      </c>
+      <c r="B30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C30" t="n">
+        <v>568</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.000167675887432569</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C31" t="n">
+        <v>569</v>
+      </c>
+      <c r="D31" t="n">
+        <v>39</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.000173819822039869</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" t="n">
+        <v>185</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.00018229560323661</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>202</v>
+      </c>
+      <c r="B33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C33" t="n">
+        <v>579</v>
+      </c>
+      <c r="D33" t="n">
+        <v>39</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.000247376437699644</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D34" t="n">
+        <v>74</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.000304917573922908</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>204</v>
+      </c>
+      <c r="B35" t="s">
+        <v>171</v>
+      </c>
+      <c r="C35" t="n">
+        <v>178</v>
+      </c>
+      <c r="D35" t="n">
+        <v>17</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.000339450293695514</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" t="s">
+        <v>171</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1660</v>
+      </c>
+      <c r="D36" t="n">
+        <v>88</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.000378286974399245</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" t="n">
+        <v>61</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.000382242725953074</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" t="n">
+        <v>434</v>
+      </c>
+      <c r="D38" t="n">
+        <v>31</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.000391870383501277</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>208</v>
+      </c>
+      <c r="B39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.000476520328532416</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>209</v>
+      </c>
+      <c r="B40" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" t="n">
+        <v>291</v>
+      </c>
+      <c r="D40" t="n">
+        <v>23</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000547012171062659</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>210</v>
+      </c>
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" t="n">
+        <v>293</v>
+      </c>
+      <c r="D41" t="n">
+        <v>23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.000601347811298845</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" t="n">
+        <v>20</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.000666336802955373</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" t="n">
+        <v>145</v>
+      </c>
+      <c r="D43" t="n">
+        <v>14</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.00098982364451621</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>213</v>
+      </c>
+      <c r="B44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1080</v>
+      </c>
+      <c r="D44" t="n">
+        <v>60</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.00110992011536811</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>214</v>
+      </c>
+      <c r="B45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" t="n">
+        <v>444</v>
+      </c>
+      <c r="D45" t="n">
+        <v>30</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.00117764658576814</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" t="s">
+        <v>171</v>
+      </c>
+      <c r="C46" t="n">
+        <v>116</v>
+      </c>
+      <c r="D46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.00122674425200959</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>216</v>
+      </c>
+      <c r="B47" t="s">
+        <v>171</v>
+      </c>
+      <c r="C47" t="n">
+        <v>527</v>
+      </c>
+      <c r="D47" t="n">
+        <v>34</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.00126566472174992</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>217</v>
+      </c>
+      <c r="B48" t="s">
+        <v>171</v>
+      </c>
+      <c r="C48" t="n">
         <v>2</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.00977551645452556</v>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.00136608107415366</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49" t="n">
+        <v>14</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.00138094918273487</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" t="s">
+        <v>171</v>
+      </c>
+      <c r="C50" t="n">
+        <v>73</v>
+      </c>
+      <c r="D50" t="n">
+        <v>9</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0014442085309053</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>171</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3528</v>
+      </c>
+      <c r="D51" t="n">
+        <v>162</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.00152350420417137</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" t="n">
+        <v>222</v>
+      </c>
+      <c r="D52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.00158354834878743</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" t="s">
+        <v>171</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5530</v>
+      </c>
+      <c r="D53" t="n">
+        <v>241</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.00159774851533998</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>223</v>
+      </c>
+      <c r="B54" t="s">
+        <v>171</v>
+      </c>
+      <c r="C54" t="n">
+        <v>205</v>
+      </c>
+      <c r="D54" t="n">
+        <v>17</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0016590857824694</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>224</v>
+      </c>
+      <c r="B55" t="s">
+        <v>171</v>
+      </c>
+      <c r="C55" t="n">
+        <v>48</v>
+      </c>
+      <c r="D55" t="n">
+        <v>7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.00180865043191427</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>225</v>
+      </c>
+      <c r="B56" t="s">
+        <v>171</v>
+      </c>
+      <c r="C56" t="n">
+        <v>138</v>
+      </c>
+      <c r="D56" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.00184906441397005</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>226</v>
+      </c>
+      <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="n">
+        <v>322</v>
+      </c>
+      <c r="D57" t="n">
+        <v>23</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.00210393674212276</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>227</v>
+      </c>
+      <c r="B58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" t="n">
+        <v>784</v>
+      </c>
+      <c r="D58" t="n">
+        <v>45</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.002450559780461</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>228</v>
+      </c>
+      <c r="B59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C59" t="n">
+        <v>111</v>
+      </c>
+      <c r="D59" t="n">
+        <v>11</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.00271748969171336</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>229</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+      <c r="C60" t="n">
+        <v>111</v>
+      </c>
+      <c r="D60" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.00271748969171336</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" t="s">
+        <v>171</v>
+      </c>
+      <c r="C61" t="n">
+        <v>254</v>
+      </c>
+      <c r="D61" t="n">
+        <v>19</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.00298282638175385</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>231</v>
+      </c>
+      <c r="B62" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" t="n">
+        <v>97</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.00312918465696206</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>232</v>
+      </c>
+      <c r="B63" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" t="n">
+        <v>164</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.00316169918739617</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>233</v>
+      </c>
+      <c r="B64" t="s">
+        <v>171</v>
+      </c>
+      <c r="C64" t="n">
+        <v>67</v>
+      </c>
+      <c r="D64" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.00320680834682948</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>234</v>
+      </c>
+      <c r="B65" t="s">
+        <v>171</v>
+      </c>
+      <c r="C65" t="n">
+        <v>82</v>
+      </c>
+      <c r="D65" t="n">
+        <v>9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.00325069875200608</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" t="s">
+        <v>171</v>
+      </c>
+      <c r="C66" t="n">
+        <v>98</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.00337224509062696</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>236</v>
+      </c>
+      <c r="B67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C67" t="n">
+        <v>183</v>
+      </c>
+      <c r="D67" t="n">
+        <v>15</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.00338360883714999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>237</v>
+      </c>
+      <c r="B68" t="s">
+        <v>171</v>
+      </c>
+      <c r="C68" t="n">
+        <v>9</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.00358099842109822</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69" t="s">
+        <v>171</v>
+      </c>
+      <c r="C69" t="n">
+        <v>9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.00358099842109822</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>239</v>
+      </c>
+      <c r="B70" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" t="n">
+        <v>376</v>
+      </c>
+      <c r="D70" t="n">
+        <v>25</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.00358988446368799</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" t="s">
+        <v>171</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>241</v>
+      </c>
+      <c r="B72" t="s">
+        <v>171</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.0039974506136657</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" t="s">
+        <v>171</v>
+      </c>
+      <c r="C73" t="n">
+        <v>360</v>
+      </c>
+      <c r="D73" t="n">
+        <v>24</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.00413341727395382</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>243</v>
+      </c>
+      <c r="B74" t="s">
+        <v>171</v>
+      </c>
+      <c r="C74" t="n">
+        <v>101</v>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.004192484728796</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>244</v>
+      </c>
+      <c r="B75" t="s">
+        <v>171</v>
+      </c>
+      <c r="C75" t="n">
+        <v>322</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.00442350112623541</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>245</v>
+      </c>
+      <c r="B76" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" t="n">
+        <v>324</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.00475518353283966</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>246</v>
+      </c>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="C77" t="n">
+        <v>10</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.00497594659010011</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>247</v>
+      </c>
+      <c r="B78" t="s">
+        <v>171</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1653</v>
+      </c>
+      <c r="D78" t="n">
+        <v>81</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.00555279531182754</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>248</v>
+      </c>
+      <c r="B79" t="s">
+        <v>171</v>
+      </c>
+      <c r="C79" t="n">
+        <v>329</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.00567565133073762</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>249</v>
+      </c>
+      <c r="B80" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" t="n">
+        <v>330</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.00587633752982829</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" t="n">
+        <v>19545</v>
+      </c>
+      <c r="D81" t="n">
+        <v>739</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.00594673219746454</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" t="n">
+        <v>15643</v>
+      </c>
+      <c r="D82" t="n">
+        <v>608</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.00625795275715939</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83" t="s">
+        <v>171</v>
+      </c>
+      <c r="C83" t="n">
+        <v>414</v>
+      </c>
+      <c r="D83" t="n">
+        <v>26</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.00632266440590331</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>253</v>
+      </c>
+      <c r="B84" t="s">
+        <v>171</v>
+      </c>
+      <c r="C84" t="n">
+        <v>91</v>
+      </c>
+      <c r="D84" t="n">
+        <v>9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.00649100656659722</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" t="n">
+        <v>91</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.00649100656659722</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>255</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" t="n">
+        <v>396</v>
+      </c>
+      <c r="D86" t="n">
+        <v>25</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.00687065030988839</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" t="n">
+        <v>143</v>
+      </c>
+      <c r="D87" t="n">
+        <v>12</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.00689987749420497</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>257</v>
+      </c>
+      <c r="B88" t="s">
+        <v>171</v>
+      </c>
+      <c r="C88" t="n">
+        <v>143</v>
+      </c>
+      <c r="D88" t="n">
+        <v>12</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.00689987749420497</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>258</v>
+      </c>
+      <c r="B89" t="s">
+        <v>171</v>
+      </c>
+      <c r="C89" t="n">
+        <v>440</v>
+      </c>
+      <c r="D89" t="n">
+        <v>27</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.00735468299273034</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>259</v>
+      </c>
+      <c r="B90" t="s">
+        <v>171</v>
+      </c>
+      <c r="C90" t="n">
+        <v>77</v>
+      </c>
+      <c r="D90" t="n">
+        <v>8</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.00750468021659253</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>260</v>
+      </c>
+      <c r="B91" t="s">
+        <v>171</v>
+      </c>
+      <c r="C91" t="n">
+        <v>359</v>
+      </c>
+      <c r="D91" t="n">
+        <v>23</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.00784183449100118</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2213</v>
+      </c>
+      <c r="D92" t="n">
+        <v>103</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.00829640066725589</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>262</v>
+      </c>
+      <c r="B93" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.00863232827404359</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>263</v>
+      </c>
+      <c r="B94" t="s">
+        <v>171</v>
+      </c>
+      <c r="C94" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.00863232827404359</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>264</v>
+      </c>
+      <c r="B95" t="s">
+        <v>171</v>
+      </c>
+      <c r="C95" t="n">
+        <v>12</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.00863232827404359</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>265</v>
+      </c>
+      <c r="B96" t="s">
+        <v>171</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4577</v>
+      </c>
+      <c r="D96" t="n">
+        <v>197</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.00865371434559104</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>266</v>
+      </c>
+      <c r="B97" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" t="n">
+        <v>35</v>
+      </c>
+      <c r="D97" t="n">
+        <v>5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.00883500020226261</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>267</v>
+      </c>
+      <c r="B98" t="s">
+        <v>171</v>
+      </c>
+      <c r="C98" t="n">
+        <v>243</v>
+      </c>
+      <c r="D98" t="n">
+        <v>17</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.00919055604142732</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>268</v>
+      </c>
+      <c r="B99" t="s">
+        <v>171</v>
+      </c>
+      <c r="C99" t="n">
+        <v>23</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.00938133246540227</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>269</v>
+      </c>
+      <c r="B100" t="s">
+        <v>171</v>
+      </c>
+      <c r="C100" t="n">
+        <v>97</v>
+      </c>
+      <c r="D100" t="n">
+        <v>9</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.00974803007987644</v>
       </c>
     </row>
   </sheetData>
@@ -3236,7 +5696,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>270</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
